--- a/data/models/northrop-grumman.xlsx
+++ b/data/models/northrop-grumman.xlsx
@@ -988,7 +988,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="12" t="n">
-        <v>553.29</v>
+        <v>552.53</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>12</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">B11*B12</f>
-        <v>79.12047</v>
+        <v>79.01179</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">B13/(B13+B14)*B10+B14/(B13+B14)*B15*(1-B16)</f>
-        <v>0.0797646695886905</v>
+        <v>0.0797557463349332</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1080,15 +1080,15 @@
       </c>
       <c r="B21" s="21" t="n">
         <f aca="false">Bear!$B$43</f>
-        <v>329.10934976155</v>
+        <v>329.166781637341</v>
       </c>
       <c r="C21" s="21" t="n">
         <f aca="false">Base!$B$43</f>
-        <v>564.011255997936</v>
+        <v>564.125926522296</v>
       </c>
       <c r="D21" s="21" t="n">
         <f aca="false">Bull!$B$43</f>
-        <v>869.87181889566</v>
+        <v>870.087017763424</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">SUMPRODUCT(B21:D21,B22:D22)</f>
-        <v>581.75092016327</v>
+        <v>581.876413111339</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1119,7 +1119,7 @@
         <v>29</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>553.29</v>
+        <v>552.53</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C25" s="23" t="n">
         <f aca="false">C23/C24-1</f>
-        <v>0.0514394262742326</v>
+        <v>0.0531127958868098</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.0797646695886905</v>
+        <v>0.0797557463349332</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1881,43 +1881,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.962355302263914</v>
+        <v>0.962359278775664</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.891263929417601</v>
+        <v>0.891274977736628</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.825424237817585</v>
+        <v>0.825441291479046</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.764448273837307</v>
+        <v>0.764470385344909</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.707976742866115</v>
+        <v>0.708003071935285</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.655676892202632</v>
+        <v>0.655706695091454</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.607240550343619</v>
+        <v>0.607273170174968</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.562382311115006</v>
+        <v>0.562417169101683</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.520837851945306</v>
+        <v>0.520874439437551</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.482362376371979</v>
+        <v>0.482400247653768</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1926,43 +1926,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>3.46632434670086</v>
+        <v>3.46633866976789</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>3.35656505515341</v>
+        <v>3.35660666392982</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>3.42642176244901</v>
+        <v>3.42649255396939</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>3.47793212462647</v>
+        <v>3.47803272309106</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>3.51036353446034</v>
+        <v>3.51049408197513</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>3.47516261367696</v>
+        <v>3.4753205724006</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>3.42342779844151</v>
+        <v>3.42361169860654</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>3.35584782722868</v>
+        <v>3.356055831813</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>3.27333357508732</v>
+        <v>3.27356351818064</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>3.1769977047287</v>
+        <v>3.17724713748136</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>33.9423763425533</v>
+        <v>33.9437634512154</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>120.679464478509</v>
+        <v>120.701107274852</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>58.2112332651515</v>
+        <v>58.2262440414729</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>92.1536096077048</v>
+        <v>92.1700074926883</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>80.6536096077048</v>
+        <v>80.6700074926883</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>564.011255997936</v>
+        <v>564.125926522296</v>
       </c>
     </row>
   </sheetData>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.0897646695886905</v>
+        <v>0.0897557463349332</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2698,43 +2698,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.957929699055533</v>
+        <v>0.957933620958361</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.879024367175607</v>
+        <v>0.87903516377875</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.806618522058874</v>
+        <v>0.806635034258934</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.740176796485168</v>
+        <v>0.740198009482225</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.679207921802541</v>
+        <v>0.679232949192202</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.623261095497705</v>
+        <v>0.623289165004725</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.571922647972192</v>
+        <v>0.57195308866319</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.524812983878485</v>
+        <v>0.524845214706858</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.481583775400395</v>
+        <v>0.481617294950742</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.441915386724877</v>
+        <v>0.441949764037049</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2743,43 +2743,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>3.40757051579312</v>
+        <v>3.40758446687999</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>3.22069317276694</v>
+        <v>3.22073273088083</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>3.04406452193206</v>
+        <v>3.0441268366459</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>2.87712250643381</v>
+        <v>2.87720496293819</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>2.71933589363409</v>
+        <v>2.71943609546749</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>2.57020258465551</v>
+        <v>2.57031833762006</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>2.42924801663312</v>
+        <v>2.42937731381779</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>2.29602365258959</v>
+        <v>2.29616466042774</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>2.17010555412837</v>
+        <v>2.17025659942121</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>2.05109303240291</v>
+        <v>2.05125259024494</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>26.7854594509695</v>
+        <v>26.7864545943441</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>71.9078324030287</v>
+        <v>71.9185703131884</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>31.7771775649321</v>
+        <v>31.7843951797955</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>58.5626370159016</v>
+        <v>58.5708497741397</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>47.0626370159016</v>
+        <v>47.0708497741397</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>329.10934976155</v>
+        <v>329.166781637341</v>
       </c>
     </row>
   </sheetData>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.0697646695886905</v>
+        <v>0.0697557463349332</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3515,43 +3515,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.966842816162154</v>
+        <v>0.966846848561994</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.903790192037181</v>
+        <v>0.903801500365375</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.844849542829523</v>
+        <v>0.844867160996208</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.789752706223095</v>
+        <v>0.78977576319715</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.738249008098897</v>
+        <v>0.738276719618458</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.690104122042788</v>
+        <v>0.690135783002664</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.645099003230424</v>
+        <v>0.645133980693371</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.603028891838853</v>
+        <v>0.603066618621728</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.563702381450594</v>
+        <v>0.563742350240119</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.52694054821172</v>
+        <v>0.526982306168062</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3560,43 +3560,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>3.51220096313452</v>
+        <v>3.51221561142933</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>3.54045664643215</v>
+        <v>3.54050094503825</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>3.77847260754699</v>
+        <v>3.77855140235819</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>3.99519755009503</v>
+        <v>3.99531419061494</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>4.18598754720986</v>
+        <v>4.1861446758677</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>4.25176897273151</v>
+        <v>4.25196403762469</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>4.28692113335246</v>
+        <v>4.2871535715121</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>4.29050365652431</v>
+        <v>4.29077207964975</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>4.26226356747166</v>
+        <v>4.26256577927887</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>4.20265105787412</v>
+        <v>4.20298410136449</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>40.3064237023726</v>
+        <v>40.3081663947383</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>181.39664279793</v>
+        <v>181.437357623424</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>95.5852463997067</v>
+        <v>95.6142771454313</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>135.891670102079</v>
+        <v>135.92244354017</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>124.391670102079</v>
+        <v>124.42244354017</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>869.87181889566</v>
+        <v>870.087017763424</v>
       </c>
     </row>
   </sheetData>
